--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45876.5</v>
+        <v>45876.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -889,6 +889,270 @@
       </c>
       <c r="AL3" s="3" t="n">
         <v>45876.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Al Buqa'a</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>45876.5625</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cardiff City</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>45876.66666666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,6 +1153,138 @@
       </c>
       <c r="AL5" s="3" t="n">
         <v>45876.66666666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <v>45876.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,138 +1153,6 @@
       </c>
       <c r="AL5" s="3" t="n">
         <v>45876.66666666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ferroviária</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>45876.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,6 +1153,402 @@
       </c>
       <c r="AL5" s="3" t="n">
         <v>45876.66666666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <v>45876.79166666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="n">
+        <v>45876.79166666666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="n">
+        <v>45876.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1548,6 +1548,138 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
+        <v>45876.79166666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="n">
         <v>45876.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1548,138 +1548,6 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45876.79166666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
         <v>45876.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,114 +1440,378 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="n">
+        <v>45876.79166666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>América Mineiro</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AL9" s="3" t="n">
+        <v>45876.79166666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL10" s="3" t="n">
         <v>45876.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1416,402 +1416,6 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45876.79166666666</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
-        <v>45876.79166666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
-        <v>45876.79166666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
         <v>45876.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -1079,43 +1079,43 @@
         <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB5" t="n">
         <v>1.9</v>
@@ -1124,22 +1124,22 @@
         <v>1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,270 +1153,6 @@
       </c>
       <c r="AL5" s="3" t="n">
         <v>45876.66666666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>45876.79166666666</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
-        <v>45876.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -897,27 +897,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45876.5625</v>
+        <v>45876.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1029,129 +1029,261 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Al Buqa'a</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>45876.5625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>England EFL League One</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Port Vale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Cardiff City</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>2.93</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>3.3</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N6" t="n">
         <v>2.1</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O6" t="n">
         <v>2.1</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P6" t="n">
         <v>9</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>1.83</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1.4</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>2.75</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2.75</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>1.4</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V6" t="n">
         <v>8</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W6" t="n">
         <v>1.08</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X6" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y6" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA6" t="n">
         <v>3.45</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB6" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD6" t="n">
         <v>3.35</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG6" t="n">
         <v>2</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH6" t="n">
         <v>6.5</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI6" t="n">
         <v>1.1</v>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AL6" s="3" t="n">
         <v>45876.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-08-07.xlsx
+++ b/jogos_2025-08-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -657,105 +652,102 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.91</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['9', '89']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45876.45833333334</v>
       </c>
     </row>
@@ -789,105 +781,102 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.55</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45876.5</v>
       </c>
     </row>
@@ -912,114 +901,111 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45876.54166666666</v>
       </c>
     </row>
@@ -1053,105 +1039,102 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="O5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.83</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['70', '72']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['2', '10', '45+7']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2.2</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AK5" s="3" t="n">
         <v>45876.5625</v>
       </c>
     </row>
@@ -1198,92 +1181,89 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
         <v>3.3</v>
       </c>
       <c r="N6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2.1</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="Z6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.83</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.5</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45876.66666666666</v>
       </c>
     </row>
